--- a/templates/test_files/Strukturvorlage_DataDictionary_KBOB_FM_v0.9.5.xlsx
+++ b/templates/test_files/Strukturvorlage_DataDictionary_KBOB_FM_v0.9.5.xlsx
@@ -17615,7 +17615,7 @@
       </c>
       <c r="C96" s="200" t="inlineStr">
         <is>
-          <t>Der Objekttyp definiert die spezifischen Informationen zu einem Typ, die allen Instanzen dieses Typs gemeinsam sind.</t>
+          <t>Optionale IFC-TypeObject-Entität zur Dokumentation des Mapping-Umfangs. Leer = Mapping gilt nur für die Objektebene. Ausgefüllt = Mapping gilt zusätzlich für die angegebene Typebene; der Wert muss ein schema-konformes Paar mit „IfcObject Entity“ bilden (z. B. IfcTank → IfcTankType). Der PredefinedType wird separat erfasst und validiert.</t>
         </is>
       </c>
       <c r="F96" s="202" t="n"/>
@@ -20924,7 +20924,11 @@
       <c r="W2" s="88" t="n"/>
       <c r="X2" s="59" t="n"/>
       <c r="Y2" s="59" t="n"/>
-      <c r="Z2" s="59" t="n"/>
+      <c r="Z2" s="59" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
       <c r="AA2" s="59" t="n"/>
       <c r="AB2" s="59" t="n"/>
       <c r="AC2" s="59" t="n"/>
@@ -21276,7 +21280,11 @@
       <c r="W6" s="88" t="n"/>
       <c r="X6" s="59" t="n"/>
       <c r="Y6" s="59" t="n"/>
-      <c r="Z6" s="59" t="n"/>
+      <c r="Z6" s="59" t="inlineStr">
+        <is>
+          <t>Leer = nur Objektebene; ausgefüllt = Mapping gilt auch für die angegebene Typebene; validiert gegen IFC 4.3 Objekt-/TypeObject-Paare</t>
+        </is>
+      </c>
       <c r="AA6" s="59" t="n"/>
       <c r="AB6" s="59" t="n"/>
       <c r="AC6" s="59" t="n"/>
@@ -21358,11 +21366,7 @@
           <t>IfcSite</t>
         </is>
       </c>
-      <c r="Z7" s="51" t="inlineStr">
-        <is>
-          <t>IfcSite</t>
-        </is>
-      </c>
+      <c r="Z7" s="51" t="n"/>
       <c r="AA7" s="51" t="n"/>
       <c r="AB7" s="51" t="n"/>
       <c r="AC7" s="51" t="n"/>
@@ -21456,11 +21460,7 @@
           <t>IfcBuilding</t>
         </is>
       </c>
-      <c r="Z8" s="51" t="inlineStr">
-        <is>
-          <t>IfcBuilding</t>
-        </is>
-      </c>
+      <c r="Z8" s="51" t="n"/>
       <c r="AA8" s="51" t="n"/>
       <c r="AB8" s="51" t="n"/>
       <c r="AC8" s="51" t="n"/>
@@ -21554,11 +21554,7 @@
           <t>IfcBuildingStorey</t>
         </is>
       </c>
-      <c r="Z9" s="51" t="inlineStr">
-        <is>
-          <t>IfcBuildingStorey</t>
-        </is>
-      </c>
+      <c r="Z9" s="51" t="n"/>
       <c r="AA9" s="51" t="n"/>
       <c r="AB9" s="51" t="n"/>
       <c r="AC9" s="51" t="n"/>
@@ -21657,7 +21653,7 @@
       </c>
       <c r="Z10" s="51" t="inlineStr">
         <is>
-          <t>IfcSpace</t>
+          <t>IfcSpaceType</t>
         </is>
       </c>
       <c r="AA10" s="51" t="n"/>
@@ -21758,7 +21754,7 @@
       </c>
       <c r="Z11" s="51" t="inlineStr">
         <is>
-          <t>IfcElement</t>
+          <t>IfcElementType</t>
         </is>
       </c>
       <c r="AA11" s="51" t="n"/>

--- a/templates/test_files/Strukturvorlage_DataDictionary_KBOB_FM_v0.9.5.xlsx
+++ b/templates/test_files/Strukturvorlage_DataDictionary_KBOB_FM_v0.9.5.xlsx
@@ -18595,7 +18595,7 @@
       </c>
       <c r="C130" s="200" t="inlineStr">
         <is>
-          <t>Beschreibt eine Liste von Merkmalen / Mebgeb für eine IFC-Entität. Merkmalssätze / Mengensätze, deren Struktur und Eigenschaften fest in der IFC-Spezifikation definiert sind.</t>
+          <t>Referenz auf einen IFC-Merkmals- oder Mengensatz. Ein Einzelwert wird direkt als Pset_*/Qto_*-Name oder zulässige absolute IRI erfasst. Mehrere Werte müssen als gültige JSON-Liste aus nicht leeren Strings mit doppelten Anführungszeichen erfasst werden, z. B. ["Pset_WallCommon", "Qto_WallBaseQuantities"]. Zeilenumbruch-, Semikolon- und einfache Kommalisten sind nicht zulässig.</t>
         </is>
       </c>
       <c r="F130" s="202" t="n"/>
@@ -23031,7 +23031,11 @@
       <c r="U6" s="59" t="n"/>
       <c r="V6" s="89" t="n"/>
       <c r="W6" s="59" t="n"/>
-      <c r="X6" s="59" t="n"/>
+      <c r="X6" s="59" t="inlineStr">
+        <is>
+          <t>Ein Wert: Pset_* / Qto_* oder zulässige absolute IRI. Mehrere Werte: strikte JSON-Liste, z. B. ["Pset_WallCommon", "Qto_WallBaseQuantities"]; keine Zeilenumbruch-/Semikolonlisten.</t>
+        </is>
+      </c>
       <c r="Y6" s="59" t="n"/>
       <c r="Z6" s="59" t="n"/>
       <c r="AA6" s="59" t="n"/>
